--- a/docs/bom/ecu25-breadboard-bom.xlsx
+++ b/docs/bom/ecu25-breadboard-bom.xlsx
@@ -670,7 +670,7 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Generated from docs/bom/breadboard-prototype.md at revision 82d5874 + uncommitted edits by hardware/kicad/gen/gen_breadboard_xlsx.py — edit the markdown, not this file.</t>
+          <t>Generated from docs/bom/breadboard-prototype.md at revision 83302c4 by hardware/kicad/gen/gen_breadboard_xlsx.py — edit the markdown, not this file.</t>
         </is>
       </c>
     </row>

--- a/docs/bom/ecu25-breadboard-bom.xlsx
+++ b/docs/bom/ecu25-breadboard-bom.xlsx
@@ -670,7 +670,7 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Generated from docs/bom/breadboard-prototype.md at revision 83302c4 by hardware/kicad/gen/gen_breadboard_xlsx.py — edit the markdown, not this file.</t>
+          <t>Generated from docs/bom/breadboard-prototype.md at revision 91caaee + uncommitted edits by hardware/kicad/gen/gen_breadboard_xlsx.py — edit the markdown, not this file.</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
     <row r="24" ht="39" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>expect a 1.41 Vpk sine on 1.65 V (≈0.24 V to 3.06 V). Run the firmware's RMS and frequency measurement and compare against a meter on the transformer output. Moving to the real board changes only the divider ratio — the maths, the filter and the code are already proven.</t>
+          <t>expect a 1.41 Vpk sine on 1.65 V (≈0.12 V to 3.06 V). Run the firmware's RMS and frequency measurement and compare against a meter on the transformer output. Moving to the real board changes only the divider ratio — the maths, the filter and the code are already proven.</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Read this before blocks F and G. Everything else runs at 24 V or below.</t>
+          <t>Read this before blocks F and G. Everything else runs at 12 V or below.</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
     <row r="22" ht="39" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>The breadboard relay's contact side switches only the 24 V rail or a low-voltage lamp. Never a mains contactor coil. The production GEN/MAINS channels are volt-free pairs on their own terminal block (J15) precisely because those coils run on a separate AC source — that circuit does not belong on a bench.</t>
+          <t>The breadboard relay's contact side switches only the 12 V rail or a low-voltage lamp. Never a mains contactor coil. The production GEN/MAINS channels are volt-free pairs on their own terminal block (J15) precisely because those coils run on a separate AC source — that circuit does not belong on a bench.</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1772,11 +1772,11 @@
       <c r="A9" s="13" t="inlineStr"/>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.3 kΩ</t>
+          <t>1.8 kΩ</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
       <c r="E9" s="13" t="inlineStr"/>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>A, B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -1797,7 +1797,7 @@
       <c r="A10" s="11" t="inlineStr"/>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>4.7 kΩ</t>
+          <t>3.3 kΩ</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
@@ -1809,20 +1809,16 @@
       <c r="E10" s="11" t="inlineStr"/>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>R26</t>
-        </is>
-      </c>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr"/>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.6 kΩ</t>
+          <t>4.7 kΩ</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
@@ -1834,12 +1830,12 @@
       <c r="E11" s="13" t="inlineStr"/>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>R304 (5.62 k)</t>
+          <t>R26</t>
         </is>
       </c>
     </row>
@@ -1847,11 +1843,11 @@
       <c r="A12" s="11" t="inlineStr"/>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>6.8 kΩ 1 %</t>
+          <t>5.6 kΩ</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>5</v>
@@ -1859,12 +1855,12 @@
       <c r="E12" s="11" t="inlineStr"/>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A, G</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>R53</t>
+          <t>R231 + JP4, R304 (5.62 k)</t>
         </is>
       </c>
     </row>
@@ -1872,24 +1868,24 @@
       <c r="A13" s="13" t="inlineStr"/>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>10 kΩ</t>
+          <t>5.6 kΩ 1/2 W</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E13" s="13" t="inlineStr"/>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>A×2, D, E×4, H×3</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>R30, R33, R34, R35, R93, R95, R96, R97, R221, R231 + JP4</t>
+          <t>R201</t>
         </is>
       </c>
     </row>
@@ -1897,24 +1893,24 @@
       <c r="A14" s="11" t="inlineStr"/>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>10 kΩ 1 %</t>
+          <t>6.8 kΩ 1 %</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="11" t="n">
         <v>5</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>8</v>
       </c>
       <c r="E14" s="11" t="inlineStr"/>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>C, D×2, F×2</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>R51, R52, R70, R90, R91</t>
+          <t>R53</t>
         </is>
       </c>
     </row>
@@ -1922,24 +1918,24 @@
       <c r="A15" s="13" t="inlineStr"/>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>10 kΩ 1/2 W</t>
+          <t>10 kΩ</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E15" s="13" t="inlineStr"/>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A, D, E×4, H×3</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>R201</t>
+          <t>R30, R33, R34, R35, R93, R95, R96, R97, R221</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1943,24 @@
       <c r="A16" s="11" t="inlineStr"/>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>47 Ω</t>
+          <t>10 kΩ 1 %</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" s="11" t="inlineStr"/>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C, D×2, F×2</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>R92</t>
+          <t>R51, R52, R70, R90, R91</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1968,7 @@
       <c r="A17" s="13" t="inlineStr"/>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>62 kΩ</t>
+          <t>47 Ω</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
@@ -1984,12 +1980,12 @@
       <c r="E17" s="13" t="inlineStr"/>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>R300–R303 (4× 330 k)</t>
+          <t>R92</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1993,7 @@
       <c r="A18" s="11" t="inlineStr"/>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>62 Ω 1 %</t>
+          <t>62 kΩ</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
@@ -2009,12 +2005,12 @@
       <c r="E18" s="11" t="inlineStr"/>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R300–R303 (4× 330 k)</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2018,7 @@
       <c r="A19" s="13" t="inlineStr"/>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>90.9 kΩ 1 %</t>
+          <t>62 Ω 1 %</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
@@ -2039,7 +2035,7 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>R71</t>
+          <t>R20</t>
         </is>
       </c>
     </row>
@@ -2047,24 +2043,24 @@
       <c r="A20" s="11" t="inlineStr"/>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>100 kΩ</t>
+          <t>90.9 kΩ 1 %</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" s="11" t="inlineStr"/>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>B, E×2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>R31, R32, R61</t>
+          <t>R71</t>
         </is>
       </c>
     </row>
@@ -2072,24 +2068,24 @@
       <c r="A21" s="13" t="inlineStr"/>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>200 Ω pot or resistance decade box</t>
+          <t>100 kΩ</t>
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E21" s="13" t="inlineStr"/>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B, E×2</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>Sender</t>
+          <t>R31, R32, R61</t>
         </is>
       </c>
     </row>
@@ -2097,14 +2093,14 @@
       <c r="A22" s="11" t="inlineStr"/>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>249 Ω 1 %</t>
+          <t>200 Ω pot or resistance decade box</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E22" s="11" t="inlineStr"/>
       <c r="F22" s="11" t="inlineStr">
@@ -2114,7 +2110,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>Sender</t>
         </is>
       </c>
     </row>
@@ -2122,11 +2118,11 @@
       <c r="A23" s="13" t="inlineStr"/>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>560 Ω</t>
+          <t>249 Ω 1 %</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="n">
         <v>5</v>
@@ -2134,62 +2130,62 @@
       <c r="E23" s="13" t="inlineStr"/>
       <c r="F23" s="13" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr"/>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>560 Ω</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="11" t="inlineStr"/>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
           <t>H×2  (optional block)</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>R73, R74</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Capacitor</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr"/>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>10 µF</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" s="11" t="inlineStr"/>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>C91 — also in the shared kit</t>
-        </is>
-      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr"/>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>22 nF C0G</t>
+          <t>1 µF film</t>
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="n">
         <v>5</v>
@@ -2197,12 +2193,12 @@
       <c r="E27" s="13" t="inlineStr"/>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>F, G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>C40, C50</t>
+          <t>C201</t>
         </is>
       </c>
     </row>
@@ -2210,24 +2206,24 @@
       <c r="A28" s="11" t="inlineStr"/>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>100 nF</t>
+          <t>10 µF</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E28" s="11" t="inlineStr"/>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>C×2, D×2</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>C20, C60, C90, C93 — also in the shared kit</t>
+          <t>C91 — also in the shared kit</t>
         </is>
       </c>
     </row>
@@ -2235,24 +2231,24 @@
       <c r="A29" s="13" t="inlineStr"/>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>100 nF film, 100 V</t>
+          <t>22 nF C0G</t>
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E29" s="13" t="inlineStr"/>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F, G</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>C30</t>
+          <t>C40, C50</t>
         </is>
       </c>
     </row>
@@ -2260,87 +2256,87 @@
       <c r="A30" s="11" t="inlineStr"/>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>470 nF film</t>
+          <t>100 nF</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E30" s="11" t="inlineStr"/>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C×2, D×2</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>C201</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+          <t>C20, C60, C90, C93 — also in the shared kit</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr"/>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>100 nF film, 100 V</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="13" t="inlineStr"/>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>C30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Diode / LED</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr"/>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>1N4148</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="E33" s="13" t="inlineStr"/>
-      <c r="F33" s="13" t="inlineStr">
-        <is>
-          <t>A×2, C×2, E×2, G×2</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>D10 (BAT54S), D20 (BAV199), D30 (BAV99), D40 (BAV199)</t>
-        </is>
-      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr"/>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>1N5819</t>
+          <t>1N4148</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E34" s="11" t="inlineStr"/>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A×2, C×2, E×2, G×2</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>D60 (SS34)</t>
+          <t>D10 (BAT54S), D20 (BAV199), D30 (BAV99), D40 (BAV199)</t>
         </is>
       </c>
     </row>
@@ -2348,24 +2344,24 @@
       <c r="A35" s="13" t="inlineStr"/>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>5.6 V bidirectional TVS (or 2× 5.1 V zeners back-to-back)</t>
+          <t>1N5819</t>
         </is>
       </c>
       <c r="C35" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E35" s="13" t="inlineStr"/>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>D50</t>
+          <t>D60 (SS34)</t>
         </is>
       </c>
     </row>
@@ -2373,66 +2369,66 @@
       <c r="A36" s="11" t="inlineStr"/>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>LED, 5 mm, any colour</t>
+          <t>5.6 V bidirectional TVS (or 2× 5.1 V zeners back-to-back)</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E36" s="11" t="inlineStr"/>
       <c r="F36" s="11" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>D50</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr"/>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>LED, 5 mm, any colour</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" s="13" t="inlineStr"/>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Transistor</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="10" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr"/>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>BC337-40</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E39" s="13" t="inlineStr"/>
-      <c r="F39" s="13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>Q60 (2N7002K)</t>
-        </is>
-      </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>BC557B</t>
+          <t>BC337-40</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
@@ -2444,58 +2440,58 @@
       <c r="E40" s="11" t="inlineStr"/>
       <c r="F40" s="11" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>Q60 (2N7002K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr"/>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>BC557B</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" s="13" t="inlineStr"/>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>Q3 (BC857)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>IC / module</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="13" t="inlineStr"/>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>25LC1024-I/P</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="13" t="inlineStr">
-        <is>
-          <t>H  (optional block)</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>U11 (M95M02-DR)</t>
-        </is>
-      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>LM358N</t>
+          <t>25LC1024-I/P</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
@@ -2507,12 +2503,12 @@
       <c r="E44" s="11" t="inlineStr"/>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H  (optional block)</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U11 (M95M02-DR)</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2516,7 @@
       <c r="A45" s="13" t="inlineStr"/>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>LM393N</t>
+          <t>LM358N</t>
         </is>
       </c>
       <c r="C45" s="13" t="n">
@@ -2532,12 +2528,12 @@
       <c r="E45" s="13" t="inlineStr"/>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>U5 (LM2903)</t>
+          <t>U3</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2541,7 @@
       <c r="A46" s="11" t="inlineStr"/>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>MAX3485 module (3.3 V)</t>
+          <t>LM393N</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
@@ -2557,12 +2553,12 @@
       <c r="E46" s="11" t="inlineStr"/>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>H  (optional block)</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>U7 (THVD1450)</t>
+          <t>U5 (LM2903)</t>
         </is>
       </c>
     </row>
@@ -2570,24 +2566,24 @@
       <c r="A47" s="13" t="inlineStr"/>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>MCP6002-I/P</t>
+          <t>MAX3485 module (3.3 V)</t>
         </is>
       </c>
       <c r="C47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="13" t="n">
         <v>2</v>
-      </c>
-      <c r="D47" s="13" t="n">
-        <v>3</v>
       </c>
       <c r="E47" s="13" t="inlineStr"/>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>D, F</t>
+          <t>H  (optional block)</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>U8, U9</t>
+          <t>U7 (THVD1450)</t>
         </is>
       </c>
     </row>
@@ -2595,146 +2591,146 @@
       <c r="A48" s="11" t="inlineStr"/>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>SN65HVD230 CAN module</t>
+          <t>MCP6002-I/P</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" s="11" t="inlineStr"/>
       <c r="F48" s="11" t="inlineStr">
         <is>
+          <t>D, F</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>U8, U9</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr"/>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>SN65HVD230 CAN module</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="13" t="inlineStr"/>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
           <t>H  (optional block)</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>U6 (TJA1051T/3)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>Relay</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="10" t="n"/>
-      <c r="G50" s="10" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="13" t="inlineStr"/>
-      <c r="B51" s="14" t="inlineStr">
-        <is>
-          <t>G5LE-1-DC24</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="n">
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr"/>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>G5LE-1-DC12</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D52" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E51" s="13" t="inlineStr"/>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr"/>
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>K1</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="B53" s="10" t="n"/>
-      <c r="C53" s="10" t="n"/>
-      <c r="D53" s="10" t="n"/>
-      <c r="E53" s="10" t="n"/>
-      <c r="F53" s="10" t="n"/>
-      <c r="G53" s="10" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr"/>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr"/>
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>Toggle switch or jumper</t>
         </is>
       </c>
-      <c r="C54" s="11" t="n">
+      <c r="C55" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D54" s="11" t="n">
+      <c r="D55" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E54" s="11" t="inlineStr"/>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr"/>
+      <c r="F55" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="G55" s="14" t="inlineStr">
         <is>
           <t>Field contact</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="B56" s="10" t="n"/>
-      <c r="C56" s="10" t="n"/>
-      <c r="D56" s="10" t="n"/>
-      <c r="E56" s="10" t="n"/>
-      <c r="F56" s="10" t="n"/>
-      <c r="G56" s="10" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="13" t="inlineStr"/>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>12 V AC transformer, plug-in, 500 mA</t>
-        </is>
-      </c>
-      <c r="C57" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="13" t="inlineStr"/>
-      <c r="F57" s="13" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>415 V line</t>
-        </is>
-      </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr"/>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>Function generator</t>
+          <t>12 V AC transformer, plug-in, 500 mA</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
@@ -2746,12 +2742,12 @@
       <c r="E58" s="11" t="inlineStr"/>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>MPU pickup</t>
+          <t>415 V line</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2755,7 @@
       <c r="A59" s="13" t="inlineStr"/>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>Split-core CT, 100 A : 5 A</t>
+          <t>Function generator</t>
         </is>
       </c>
       <c r="C59" s="13" t="n">
@@ -2771,12 +2767,12 @@
       <c r="E59" s="13" t="inlineStr"/>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>Field CT</t>
+          <t>MPU pickup</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2780,7 @@
       <c r="A60" s="11" t="inlineStr"/>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>USB-CAN adapter (CANable / SocketCAN)</t>
+          <t>Split-core CT, 100 A : 5 A</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
@@ -2796,10 +2792,35 @@
       <c r="E60" s="11" t="inlineStr"/>
       <c r="F60" s="11" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>Field CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr"/>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>USB-CAN adapter (CANable / SocketCAN)</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="13" t="inlineStr"/>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
           <t>H  (optional block)</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr"/>
+      <c r="G61" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G4"/>
@@ -2926,12 +2947,12 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>24 V 2 A bench supply with adjustable current limit</t>
+          <t>12 V 2 A bench supply with adjustable current limit</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>The genset rail. The limit is the safety feature</t>
+          <t>The genset rail — the real set is 12 V / 75 Ah. The limit is the safety feature</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2964,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>24 V → 5 V buck module (LM2596 or MP1584)</t>
+          <t>12 V → 5 V buck module (LM2596 or MP1584)</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -3115,14 +3136,14 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>• 24 V, 5 V and 3.3 V (from the dev board) with a single common ground shared by the dev board and the 24 V supply. A missing ground bond between two supplies is the most common first-time analog fault.</t>
+          <t>• 12 V, 5 V and 3.3 V (from the dev board) with a single common ground shared by the dev board and the 12 V supply. A missing ground bond between two supplies is the most common first-time analog fault.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="39" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>• 100 nF from every IC's supply pin to ground, within one row of the pin, plus 10 µF bulk per rail per breadboard. The production board carries C63–C67 for exactly this. An undecoupled LM358 on 24 V, or an MCP6002 driving 10 µF, fed from a switching buck module, will oscillate — and you will blame the topology.</t>
+          <t>• 100 nF from every IC's supply pin to ground, within one row of the pin, plus 10 µF bulk per rail per breadboard. The production board carries C63–C67 for exactly this. An undecoupled LM358 on 12 V, or an MCP6002 driving 10 µF, fed from a switching buck module, will oscillate — and you will blame the topology.</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3198,7 @@
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>+24 V → switch → R201 → node; node → R211 → GND; node → C201 → GND; node → R221 → MCU pin; clamp diodes at the MCU pin.</t>
+          <t>+12 V → switch → R201 → node; node → R211 → GND; node → C201 → GND; node → R221 → MCU pin; clamp diodes at the MCU pin.</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3232,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>10 kΩ 1/2 W</t>
+          <t>5.6 kΩ 1/2 W</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -3221,7 +3242,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Top of divider — the 1/2 W rating is real, it eats the 24 V surge energy</t>
+          <t>Top of divider — the 1/2 W rating is real, it eats the surge energy</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3254,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.3 kΩ</t>
+          <t>1.8 kΩ</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -3243,7 +3264,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Bottom of divider → 5.95 V at the node</t>
+          <t>Bottom of divider → 2.92 V at the node, 1.6 mA wetting current</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3276,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>470 nF film</t>
+          <t>1 µF film</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -3265,7 +3286,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Debounce on the divider node, τ ≈ 1.17 ms</t>
+          <t>Debounce on the divider node, τ ≈ 1.4 ms</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3342,7 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>10 kΩ (optional)</t>
+          <t>5.6 kΩ (optional)</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -3331,7 +3352,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Pull-up from the input terminal to +24 V, for ground-switched contacts — many panel switches close to ground rather than feeding 24 V in. Fit the pull-up or the field 24 V feed, never both</t>
+          <t>Pull-up from the input terminal to +12 V, for ground-switched contacts — many panel switches close to ground rather than feeding 12 V in. Fit the pull-up or the field 12 V feed, never both</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3384,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>5.95 V at the node with the switch closed, 0 V open; clamped pin sits near 4.0 V with ~0.2 mA injection, both inside the STM32's limits. Then read it in firmware and confirm the debounce rejects a deliberately bouncy contact. Build one channel — the other seven are identical.</t>
+          <t>2.92 V at the node with the switch closed, 0 V open; clamped pin sits near 4.0 V with ~0.2 mA injection, both inside the STM32's limits. Then read it in firmware and confirm the debounce rejects a deliberately bouncy contact. Build one channel — the other seven are identical.</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3458,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Coil (pin 5 → +24 V, pin 2 → driver collector/drain)</t>
+          <t>Coil (pin 5 → +12 V, pin 2 → driver collector/drain)</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3508,7 @@
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>MCU pin → R60 → base; base → R61 → GND; emitter → GND; collector → relay pin 2; relay pin 5 → +24 V; flyback cathode → +24 V, anode → drain; relay pin 1 (COM) → +24 V; pin 3 (NO) → load.</t>
+          <t>MCU pin → R60 → base; base → R61 → GND; emitter → GND; collector → relay pin 2; relay pin 5 → +24 V; flyback cathode → +12 V, anode → drain; relay pin 1 (COM) → +24 V; pin 3 (NO) → load.</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3542,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>G5LE-1-DC24</t>
+          <t>G5LE-1-DC12</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -3597,7 +3618,7 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Base resistor. The relay coil is 1.44 kΩ / 16.7 mA, so at hFE ≥ 100 the base needs 0.17 mA; 3.3 V through 1 kΩ gives 2.6 mA — 15× overdrive, hard saturation. The production 100 Ω is a MOSFET gate-stopper and has no function on a BJT: fit the 1 kΩ instead, not both</t>
+          <t>Base resistor. The relay coil is 360 Ω / 33.3 mA, so at hFE ≥ 100 the base needs 0.33 mA; 3.3 V through 1 kΩ gives 2.6 mA — 15× overdrive, hard saturation. The production 100 Ω is a MOSFET gate-stopper and has no function on a BJT: fit the 1 kΩ instead, not both</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4023,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Filter → clamp and ADC pin. This is the resistor that makes the fault survival true: with the sender shorted to +24 V it holds clamp current to ~3.6 mA, against the STM32's ±5 mA injection limit. Without it the fault drives 20 mA into the pin</t>
+          <t>Filter → clamp and ADC pin. This is the resistor that makes the fault survival true: with the sender shorted to +12 V it holds clamp current to ~3.6 mA, against the STM32's ±5 mA injection limit. Without it the fault drives 20 mA into the pin</t>
         </is>
       </c>
     </row>

--- a/docs/bom/ecu25-breadboard-bom.xlsx
+++ b/docs/bom/ecu25-breadboard-bom.xlsx
@@ -670,7 +670,7 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Generated from docs/bom/breadboard-prototype.md at revision 91caaee + uncommitted edits by hardware/kicad/gen/gen_breadboard_xlsx.py — edit the markdown, not this file.</t>
+          <t>Generated from docs/bom/breadboard-prototype.md at revision 6a780e9 + uncommitted edits by hardware/kicad/gen/gen_breadboard_xlsx.py — edit the markdown, not this file.</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>MCU pin → R60 → base; base → R61 → GND; emitter → GND; collector → relay pin 2; relay pin 5 → +24 V; flyback cathode → +12 V, anode → drain; relay pin 1 (COM) → +24 V; pin 3 (NO) → load.</t>
+          <t>MCU pin → R60 → base; base → R61 → GND; emitter → GND; collector → relay pin 2; relay pin 5 → +12 V; flyback cathode → +12 V, anode → drain; relay pin 1 (COM) → +12 V; pin 3 (NO) → load.</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Flyback, cathode to +24 V</t>
+          <t>Flyback, cathode to +12 V</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Optional indicator, from NO (pin 3) to GND, with COM (pin 1) tied to +24 V — in series with the 3.3 kΩ below. In parallel with the contacts it would light when the relay is open</t>
+          <t>Optional indicator, from NO (pin 3) to GND, with COM (pin 1) tied to +12 V — in series with the 3.3 kΩ below. In parallel with the contacts it would light when the relay is open</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Runs from +24 V — its input common-mode range (V+ − 1.5 V) must clear the 4.5 V reference, which it does</t>
+          <t>Runs from +12 V — its input common-mode range (V+ − 1.5 V) must clear the 4.5 V reference, which it does</t>
         </is>
       </c>
     </row>

--- a/docs/bom/ecu25-breadboard-bom.xlsx
+++ b/docs/bom/ecu25-breadboard-bom.xlsx
@@ -670,7 +670,7 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Generated from docs/bom/breadboard-prototype.md at revision 6a780e9 + uncommitted edits by hardware/kicad/gen/gen_breadboard_xlsx.py — edit the markdown, not this file.</t>
+          <t>Generated from docs/bom/breadboard-prototype.md at revision d78e694 + uncommitted edits by hardware/kicad/gen/gen_breadboard_xlsx.py — edit the markdown, not this file.</t>
         </is>
       </c>
     </row>
@@ -1726,20 +1726,20 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="13" t="inlineStr"/>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>B, C×2, G</t>
+          <t>A, B, C×2, G</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>R18, R23, R60 (100 Ω), R305</t>
+          <t>R18, R23, R60 (100 Ω), R231 + JP4, R305</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>5</v>
@@ -1855,12 +1855,12 @@
       <c r="E12" s="11" t="inlineStr"/>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>A, G</t>
+          <t>G</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>R231 + JP4, R304 (5.62 k)</t>
+          <t>R304 (5.62 k)</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>5.6 kΩ (optional)</t>
+          <t>1 kΩ (optional)</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
